--- a/data/trans_orig/KIDMED_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>36848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>44120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>53030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77228</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57559</t>
+          <t>57388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>267628</t>
+          <t>269758</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217711</t>
+          <t>213552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292096</t>
+          <t>293303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>414</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>312627</t>
+          <t>314792</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284989</t>
+          <t>285979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336131</t>
+          <t>338106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>814</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>580255</t>
+          <t>584550</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>522071</t>
+          <t>525318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>613902</t>
+          <t>619729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172767</t>
+          <t>170636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148249</t>
+          <t>147194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224742</t>
+          <t>226162</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>176961</t>
+          <t>174796</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154016</t>
+          <t>152020</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>205890</t>
+          <t>204213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>405</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>349728</t>
+          <t>345433</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314642</t>
+          <t>310431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>411293</t>
+          <t>405836</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37429</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1632,107 +1632,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92760</t>
+          <t>93581</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82321</t>
+          <t>82758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100993</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>147</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110512</t>
+          <t>113226</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98136</t>
+          <t>100565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122733</t>
+          <t>125650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>203271</t>
+          <t>206806</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>190799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>219734</t>
+          <t>222083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -1745,107 +1745,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40695</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>57445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63017</t>
+          <t>60303</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51485</t>
+          <t>48621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75375</t>
+          <t>72411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>149</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111851</t>
+          <t>108316</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96584</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -2088,107 +2088,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>389645</t>
+          <t>392597</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333089</t>
+          <t>342604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>416025</t>
+          <t>420711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>461237</t>
+          <t>466116</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>428847</t>
+          <t>435981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>487817</t>
+          <t>495052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>850883</t>
+          <t>858713</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>787851</t>
+          <t>803647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>888769</t>
+          <t>896420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>245517</t>
+          <t>242566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219876</t>
+          <t>213803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302750</t>
+          <t>293572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>258966</t>
+          <t>254087</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232911</t>
+          <t>224987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>290726</t>
+          <t>285754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>603</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>504483</t>
+          <t>496653</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>466286</t>
+          <t>457744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569634</t>
+          <t>554870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>54605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KIDMED_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
+          <t>Menores según tipo de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36513</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30746</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42185</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29258</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19047</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>28905</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>65418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16007</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10608</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22005</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23916</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16510</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34490</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,54%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>42903</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57388</t>
+          <t>40266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>296099</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>272031</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>316961</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>269758</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>213552</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>293303</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>314792</t>
+          <t>268959</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285979</t>
+          <t>251339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338106</t>
+          <t>284565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>584550</t>
+          <t>565059</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>525318</t>
+          <t>536532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>619729</t>
+          <t>590245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156321</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>135256</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>180694</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>170636</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>147194</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>226162</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>174796</t>
+          <t>143882</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152020</t>
+          <t>128673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>204213</t>
+          <t>161813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>345433</t>
+          <t>300203</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>310431</t>
+          <t>274385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>405836</t>
+          <t>328968</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14003</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8371</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22744</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11438</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6524</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18070</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,22 +1477,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37792</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>106411</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>95211</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116467</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>63,84%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>69,87%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>93581</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>82758</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>102150</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>56,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>69,88%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>84844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125650</t>
+          <t>104672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>206806</t>
+          <t>201689</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>190799</t>
+          <t>186882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222083</t>
+          <t>215765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53102</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43488</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63844</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48014</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>38815</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57445</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,84%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60303</t>
+          <t>47034</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48621</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72411</t>
+          <t>57765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>108316</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>86272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123530</t>
+          <t>115168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12834</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9186</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>584</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>392597</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>342604</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>420711</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393143</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>371438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>411937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>858713</t>
+          <t>832165</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>803647</t>
+          <t>797550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>896420</t>
+          <t>862427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>225430</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>201867</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>254502</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>242566</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>213803</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>293572</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,81%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>207319</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224987</t>
+          <t>188169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>285754</t>
+          <t>227536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>496653</t>
+          <t>432750</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>457744</t>
+          <t>400925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>554870</t>
+          <t>465779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24584</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>29610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>51442</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
